--- a/data/eval/S2_post.xlsx
+++ b/data/eval/S2_post.xlsx
@@ -8,14 +8,27 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\apoorva.ajay\Downloads\ApoorvaThesis\ApoorvaThesis\enrichment_api\data\eval\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09034492-8647-49AB-992B-496F7EBB02F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE0325BB-7432-4019-B572-176AF685F6F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="360" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -4725,10 +4738,14 @@
   <dimension ref="A1:CG101"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
+    <col min="10" max="10" width="36.88671875" customWidth="1"/>
+    <col min="11" max="11" width="33.44140625" customWidth="1"/>
     <col min="24" max="24" width="17.44140625" customWidth="1"/>
     <col min="26" max="26" width="8.88671875" style="1"/>
     <col min="27" max="27" width="16" customWidth="1"/>
     <col min="28" max="30" width="0" hidden="1" customWidth="1"/>
+    <col min="81" max="81" width="32.77734375" customWidth="1"/>
+    <col min="85" max="85" width="32.109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:85" x14ac:dyDescent="0.3">
